--- a/data/gravel/Scott Addict Gravel RC 2025.xlsx
+++ b/data/gravel/Scott Addict Gravel RC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE645D11-74A7-2645-BD9D-E3F80BD1295B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CE3936-25B2-C34A-AEF9-14A809463505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31540" yWindow="-19460" windowWidth="27600" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3580" yWindow="860" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="169">
   <si>
     <t>brand</t>
   </si>
@@ -524,6 +524,9 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>https://asset.scott-sports.com/fit-in/2000x2000/423/4232047969_2136124_2.png?signature=1ad7a2a05254d0c8d5879a6a98c8f345231395bd09d4534f0a3bbeaf54f10e70</t>
   </si>
 </sst>
 </file>
@@ -941,6 +944,11 @@
         <v>166</v>
       </c>
     </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>168</v>
+      </c>
+    </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Scott Addict Gravel RC 2025.xlsx
+++ b/data/gravel/Scott Addict Gravel RC 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CE3936-25B2-C34A-AEF9-14A809463505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD21C41-F972-1949-9E1F-8337D8DD2B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3580" yWindow="860" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -520,13 +520,13 @@
     <t>trail</t>
   </si>
   <si>
-    <t>https://www.scott-sports.com/us/en/product/scott-addict-gravel-rc-bike?article=4232047969004</t>
-  </si>
-  <si>
     <t>a8:g33</t>
   </si>
   <si>
     <t>https://asset.scott-sports.com/fit-in/2000x2000/423/4232047969_2136124_2.png?signature=1ad7a2a05254d0c8d5879a6a98c8f345231395bd09d4534f0a3bbeaf54f10e70</t>
+  </si>
+  <si>
+    <t>https://www.scott-sports.com/us/en/all-about-gravel</t>
   </si>
 </sst>
 </file>
@@ -941,12 +941,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">

--- a/data/gravel/Scott Addict Gravel RC 2025.xlsx
+++ b/data/gravel/Scott Addict Gravel RC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD21C41-F972-1949-9E1F-8337D8DD2B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D083A3F3-D188-2F41-8879-8A91DBCCD570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="171">
   <si>
     <t>brand</t>
   </si>
@@ -301,9 +301,6 @@
     <t>Addict Gravel RC</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -527,6 +524,15 @@
   </si>
   <si>
     <t>https://www.scott-sports.com/us/en/all-about-gravel</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Givisiez, Switzerland</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -897,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -941,12 +947,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -954,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -962,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>8</v>
@@ -1028,7 +1034,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>14</v>
@@ -1038,19 +1044,19 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="R9" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="S9" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="R9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="T9" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U9" s="4"/>
       <c r="W9" s="4"/>
@@ -1079,7 +1085,7 @@
         <v>187</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>16</v>
@@ -1089,19 +1095,19 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q10" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="R10" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="S10" s="4" t="s">
+      <c r="T10" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -1127,7 +1133,7 @@
         <v>592.5</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>18</v>
@@ -1137,19 +1143,19 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q11" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="R11" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="T11" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -1175,7 +1181,7 @@
         <v>847</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>20</v>
@@ -1185,19 +1191,19 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q12" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="R12" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="S12" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="S12" s="4" t="s">
+      <c r="T12" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="T12" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -1223,7 +1229,7 @@
         <v>71</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>22</v>
@@ -1233,24 +1239,24 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>23</v>
@@ -1271,7 +1277,7 @@
         <v>283</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>23</v>
@@ -1281,19 +1287,19 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -1319,7 +1325,7 @@
         <v>1063.5</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>25</v>
@@ -1329,24 +1335,24 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q15" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="R15" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="S15" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="S15" s="4" t="s">
+      <c r="T15" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="T15" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>26</v>
@@ -1367,7 +1373,7 @@
         <v>536</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>26</v>
@@ -1377,19 +1383,19 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q16" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="R16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="S16" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="T16" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -1415,7 +1421,7 @@
         <v>566</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>28</v>
@@ -1425,19 +1431,19 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="R17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="S17" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="T17" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="T17" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -1463,7 +1469,7 @@
         <v>73</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>30</v>
@@ -1473,19 +1479,19 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q18" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="R18" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="S18" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="S18" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="T18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U18" s="4"/>
       <c r="Y18" s="4"/>
@@ -1513,7 +1519,7 @@
         <v>425</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>32</v>
@@ -1523,19 +1529,19 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -1561,7 +1567,7 @@
         <v>406.1</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>34</v>
@@ -1571,19 +1577,19 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q20" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="R20" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="R20" s="4" t="s">
+      <c r="S20" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="S20" s="4" t="s">
+      <c r="T20" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -1609,7 +1615,7 @@
         <v>609.70000000000005</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>36</v>
@@ -1619,19 +1625,19 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q21" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="Q21" s="4" t="s">
+      <c r="R21" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="S21" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="S21" s="4" t="s">
+      <c r="T21" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="T21" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -1639,7 +1645,7 @@
         <v>40</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="3">
         <v>83</v>
@@ -1657,34 +1663,34 @@
         <v>113</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q22" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="R22" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="S22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="T22" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="T22" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1734,7 +1740,7 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3">
@@ -2163,7 +2169,15 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>93</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Scott Addict Gravel RC 2025.xlsx
+++ b/data/gravel/Scott Addict Gravel RC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D083A3F3-D188-2F41-8879-8A91DBCCD570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81342C0-20A4-A446-8B77-94AE91292260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="177">
   <si>
     <t>brand</t>
   </si>
@@ -533,6 +533,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -903,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -2030,153 +2048,183 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>67</v>
-      </c>
-      <c r="B56">
-        <v>180</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>68</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>75</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>82</v>
-      </c>
-      <c r="B71">
-        <v>8999</v>
+        <v>76</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>84</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77">
+        <v>8999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>168</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>169</v>
       </c>
     </row>
